--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_maule.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.15206334006426</v>
+      </c>
+      <c r="C2">
         <v>31.86502071320024</v>
-      </c>
-      <c r="C2">
-        <v>26.15206334006426</v>
       </c>
       <c r="D2">
         <v>3.138237407721957</v>
       </c>
       <c r="E2">
-        <v>20.16555418935535</v>
+        <v>16.55014930616547</v>
       </c>
       <c r="F2">
         <v>63.28429650447918</v>
       </c>
       <c r="G2">
-        <v>16.55014930616547</v>
+        <v>20.16555418935535</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.36043670062522</v>
+      </c>
+      <c r="C3">
         <v>28.69021549398584</v>
-      </c>
-      <c r="C3">
-        <v>27.36043670062522</v>
       </c>
       <c r="D3">
         <v>3.485508849557522</v>
       </c>
       <c r="E3">
+        <v>17.53304860687411</v>
+      </c>
+      <c r="F3">
+        <v>64.0817571690055</v>
+      </c>
+      <c r="G3">
         <v>18.3851942241204</v>
-      </c>
-      <c r="F3">
-        <v>64.08175716900548</v>
-      </c>
-      <c r="G3">
-        <v>17.53304860687411</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.15918295474555</v>
+      </c>
+      <c r="C4">
         <v>55.13294594118683</v>
-      </c>
-      <c r="C4">
-        <v>24.15918295474555</v>
       </c>
       <c r="D4">
         <v>1.813797508783136</v>
       </c>
       <c r="E4">
-        <v>30.75034374386172</v>
+        <v>13.4747593792968</v>
       </c>
       <c r="F4">
         <v>55.77489687684149</v>
       </c>
       <c r="G4">
-        <v>13.4747593792968</v>
+        <v>30.75034374386172</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>31.40311804008908</v>
+      </c>
+      <c r="C5">
         <v>37.01559020044544</v>
-      </c>
-      <c r="C5">
-        <v>31.40311804008908</v>
       </c>
       <c r="D5">
         <v>2.701564380264741</v>
       </c>
       <c r="E5">
-        <v>21.97831261571013</v>
+        <v>18.64586088336419</v>
       </c>
       <c r="F5">
         <v>59.37582650092568</v>
       </c>
       <c r="G5">
-        <v>18.64586088336419</v>
+        <v>21.97831261571013</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>34.53926022063595</v>
+      </c>
+      <c r="C6">
         <v>19.48085658663206</v>
-      </c>
-      <c r="C6">
-        <v>34.53926022063595</v>
       </c>
       <c r="D6">
         <v>5.133244503664224</v>
       </c>
       <c r="E6">
-        <v>12.64825465040342</v>
+        <v>22.42516168446776</v>
       </c>
       <c r="F6">
         <v>64.92658366512882</v>
       </c>
       <c r="G6">
-        <v>22.42516168446776</v>
+        <v>12.64825465040342</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.2296635086573</v>
+      </c>
+      <c r="C7">
         <v>39.12120222149624</v>
-      </c>
-      <c r="C7">
-        <v>27.2296635086573</v>
       </c>
       <c r="D7">
         <v>2.55615866388309</v>
       </c>
       <c r="E7">
-        <v>23.51728201099764</v>
+        <v>16.3688138256088</v>
       </c>
       <c r="F7">
         <v>60.11390416339356</v>
       </c>
       <c r="G7">
-        <v>16.3688138256088</v>
+        <v>23.51728201099764</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>21.71438427043808</v>
+      </c>
+      <c r="C8">
         <v>40.03104518799586</v>
-      </c>
-      <c r="C8">
-        <v>21.71438427043808</v>
       </c>
       <c r="D8">
         <v>2.498061180525636</v>
       </c>
       <c r="E8">
-        <v>24.74941352100662</v>
+        <v>13.42503732139049</v>
       </c>
       <c r="F8">
         <v>61.82554915760291</v>
       </c>
       <c r="G8">
-        <v>13.42503732139049</v>
+        <v>24.74941352100662</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>27.68186003683241</v>
+      </c>
+      <c r="C9">
         <v>36.92449355432781</v>
-      </c>
-      <c r="C9">
-        <v>27.68186003683241</v>
       </c>
       <c r="D9">
         <v>2.708229426433915</v>
       </c>
       <c r="E9">
-        <v>22.43199776239424</v>
+        <v>16.81700580378995</v>
       </c>
       <c r="F9">
         <v>60.75099643381582</v>
       </c>
       <c r="G9">
-        <v>16.81700580378995</v>
+        <v>22.43199776239424</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.58580413297395</v>
+      </c>
+      <c r="C10">
         <v>34.32884097035041</v>
-      </c>
-      <c r="C10">
-        <v>28.58580413297395</v>
       </c>
       <c r="D10">
         <v>2.913002512562814</v>
       </c>
       <c r="E10">
-        <v>21.07167280668858</v>
+        <v>17.54649136352607</v>
       </c>
       <c r="F10">
         <v>61.38183582978536</v>
       </c>
       <c r="G10">
-        <v>17.54649136352607</v>
+        <v>21.07167280668858</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.29546792230724</v>
+      </c>
+      <c r="C11">
         <v>35.12360211889347</v>
-      </c>
-      <c r="C11">
-        <v>27.29546792230724</v>
       </c>
       <c r="D11">
         <v>2.847088395475492</v>
       </c>
       <c r="E11">
-        <v>21.62529443739808</v>
+        <v>16.80558072114513</v>
       </c>
       <c r="F11">
         <v>61.56912484145678</v>
       </c>
       <c r="G11">
-        <v>16.80558072114513</v>
+        <v>21.62529443739808</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.07931099753927</v>
+      </c>
+      <c r="C12">
         <v>42.24115086125308</v>
-      </c>
-      <c r="C12">
-        <v>27.07931099753927</v>
       </c>
       <c r="D12">
         <v>2.367359741889227</v>
       </c>
       <c r="E12">
-        <v>24.94745785449179</v>
+        <v>15.99293475830613</v>
       </c>
       <c r="F12">
         <v>59.05960738720209</v>
       </c>
       <c r="G12">
-        <v>15.99293475830613</v>
+        <v>24.94745785449179</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.5801002413217</v>
+      </c>
+      <c r="C13">
         <v>42.34267681455356</v>
-      </c>
-      <c r="C13">
-        <v>25.5801002413217</v>
       </c>
       <c r="D13">
         <v>2.361683472161333</v>
       </c>
       <c r="E13">
-        <v>25.21556489055937</v>
+        <v>15.233252266195</v>
       </c>
       <c r="F13">
         <v>59.55118284324563</v>
       </c>
       <c r="G13">
-        <v>15.233252266195</v>
+        <v>25.21556489055937</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.72918678771489</v>
+      </c>
+      <c r="C14">
         <v>42.93992659841607</v>
-      </c>
-      <c r="C14">
-        <v>25.72918678771489</v>
       </c>
       <c r="D14">
         <v>2.328834907782276</v>
       </c>
       <c r="E14">
-        <v>25.45808520384792</v>
+        <v>15.25423728813559</v>
       </c>
       <c r="F14">
         <v>59.28767750801649</v>
       </c>
       <c r="G14">
-        <v>15.25423728813559</v>
+        <v>25.45808520384792</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.96802056162276</v>
+      </c>
+      <c r="C15">
         <v>28.64581840418112</v>
-      </c>
-      <c r="C15">
-        <v>26.96802056162276</v>
       </c>
       <c r="D15">
         <v>3.490910910243154</v>
       </c>
       <c r="E15">
-        <v>18.40827178004139</v>
+        <v>17.33009142429098</v>
       </c>
       <c r="F15">
-        <v>64.26163679566764</v>
+        <v>64.26163679566763</v>
       </c>
       <c r="G15">
-        <v>17.33009142429099</v>
+        <v>18.40827178004138</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>24.59333225962313</v>
+      </c>
+      <c r="C16">
         <v>44.32275728780802</v>
-      </c>
-      <c r="C16">
-        <v>24.59333225962313</v>
       </c>
       <c r="D16">
         <v>2.256177325581395</v>
       </c>
       <c r="E16">
+        <v>14.55949656750572</v>
+      </c>
+      <c r="F16">
+        <v>59.20099160945843</v>
+      </c>
+      <c r="G16">
         <v>26.23951182303585</v>
-      </c>
-      <c r="F16">
-        <v>59.20099160945842</v>
-      </c>
-      <c r="G16">
-        <v>14.55949656750572</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>25.24157435776574</v>
+      </c>
+      <c r="C17">
         <v>39.40608060334669</v>
-      </c>
-      <c r="C17">
-        <v>25.24157435776574</v>
       </c>
       <c r="D17">
         <v>2.537679425837321</v>
       </c>
       <c r="E17">
-        <v>23.93358144861151</v>
+        <v>15.33066132264529</v>
       </c>
       <c r="F17">
         <v>60.7357572287432</v>
       </c>
       <c r="G17">
-        <v>15.33066132264529</v>
+        <v>23.93358144861151</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>28.32839463134042</v>
+      </c>
+      <c r="C18">
         <v>34.26878159316716</v>
-      </c>
-      <c r="C18">
-        <v>28.32839463134042</v>
       </c>
       <c r="D18">
         <v>2.918107833163784</v>
       </c>
       <c r="E18">
-        <v>21.0758774468815</v>
+        <v>17.42243948457366</v>
       </c>
       <c r="F18">
         <v>61.50168306854485</v>
       </c>
       <c r="G18">
-        <v>17.42243948457366</v>
+        <v>21.0758774468815</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.70650813516896</v>
+      </c>
+      <c r="C19">
         <v>37.28097622027534</v>
-      </c>
-      <c r="C19">
-        <v>27.70650813516896</v>
       </c>
       <c r="D19">
         <v>2.68233319345363</v>
       </c>
       <c r="E19">
-        <v>22.59624502180922</v>
+        <v>16.79309690878058</v>
       </c>
       <c r="F19">
-        <v>60.61065806941021</v>
+        <v>60.6106580694102</v>
       </c>
       <c r="G19">
-        <v>16.79309690878058</v>
+        <v>22.59624502180921</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>27.03477617462079</v>
+      </c>
+      <c r="C20">
         <v>31.779504254532</v>
-      </c>
-      <c r="C20">
-        <v>27.03477617462079</v>
       </c>
       <c r="D20">
         <v>3.146682188591385</v>
       </c>
       <c r="E20">
-        <v>20.01048279075185</v>
+        <v>17.02288742647487</v>
       </c>
       <c r="F20">
         <v>62.96662978277327</v>
       </c>
       <c r="G20">
-        <v>17.02288742647487</v>
+        <v>20.01048279075185</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>25.54024161987409</v>
+      </c>
+      <c r="C21">
         <v>35.27309851965288</v>
-      </c>
-      <c r="C21">
-        <v>25.54024161987409</v>
       </c>
       <c r="D21">
         <v>2.835021707670043</v>
       </c>
       <c r="E21">
-        <v>21.93418685853349</v>
+        <v>15.88191725743308</v>
       </c>
       <c r="F21">
         <v>62.18389588403344</v>
       </c>
       <c r="G21">
-        <v>15.88191725743308</v>
+        <v>21.93418685853349</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.43728701769814</v>
+      </c>
+      <c r="C22">
         <v>34.21457623392327</v>
-      </c>
-      <c r="C22">
-        <v>26.43728701769814</v>
       </c>
       <c r="D22">
         <v>2.922730923694779</v>
       </c>
       <c r="E22">
-        <v>21.29734168120702</v>
+        <v>16.45625919463546</v>
       </c>
       <c r="F22">
         <v>62.24639912415751</v>
       </c>
       <c r="G22">
-        <v>16.45625919463546</v>
+        <v>21.29734168120702</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>23.42617321632964</v>
+      </c>
+      <c r="C23">
         <v>42.27394124380008</v>
-      </c>
-      <c r="C23">
-        <v>23.42617321632964</v>
       </c>
       <c r="D23">
         <v>2.365523465703971</v>
       </c>
       <c r="E23">
-        <v>25.51231867372784</v>
+        <v>14.13769283905135</v>
       </c>
       <c r="F23">
         <v>60.34998848722081</v>
       </c>
       <c r="G23">
-        <v>14.13769283905135</v>
+        <v>25.51231867372784</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>26.46578383950519</v>
+      </c>
+      <c r="C24">
         <v>34.35889302989454</v>
-      </c>
-      <c r="C24">
-        <v>26.46578383950519</v>
       </c>
       <c r="D24">
         <v>2.91045465035772</v>
       </c>
       <c r="E24">
-        <v>21.36419217418744</v>
+        <v>16.45629536131272</v>
       </c>
       <c r="F24">
         <v>62.17951246449984</v>
       </c>
       <c r="G24">
-        <v>16.45629536131272</v>
+        <v>21.36419217418744</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.0466949215555</v>
+      </c>
+      <c r="C25">
         <v>35.6457729199197</v>
-      </c>
-      <c r="C25">
-        <v>28.0466949215555</v>
       </c>
       <c r="D25">
         <v>2.805381727158949</v>
       </c>
       <c r="E25">
-        <v>21.77606177606178</v>
+        <v>17.13377242789007</v>
       </c>
       <c r="F25">
         <v>61.09016579604815</v>
       </c>
       <c r="G25">
-        <v>17.13377242789007</v>
+        <v>21.77606177606178</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>26.45483936148717</v>
+      </c>
+      <c r="C26">
         <v>35.66377045867852</v>
-      </c>
-      <c r="C26">
-        <v>26.45483936148717</v>
       </c>
       <c r="D26">
         <v>2.803966005665723</v>
       </c>
       <c r="E26">
-        <v>21.99856666562802</v>
+        <v>16.31820023057988</v>
       </c>
       <c r="F26">
         <v>61.68323310379211</v>
       </c>
       <c r="G26">
-        <v>16.31820023057988</v>
+        <v>21.99856666562802</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.43825558110213</v>
+      </c>
+      <c r="C27">
         <v>37.84024326930208</v>
-      </c>
-      <c r="C27">
-        <v>27.43825558110213</v>
       </c>
       <c r="D27">
         <v>2.642689141513132</v>
       </c>
       <c r="E27">
-        <v>22.8948372186946</v>
+        <v>16.60122506675043</v>
       </c>
       <c r="F27">
         <v>60.50393771455496</v>
       </c>
       <c r="G27">
-        <v>16.60122506675043</v>
+        <v>22.8948372186946</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.7236564377334</v>
+      </c>
+      <c r="C28">
         <v>38.39909076148725</v>
-      </c>
-      <c r="C28">
-        <v>27.7236564377334</v>
       </c>
       <c r="D28">
         <v>2.604228329809725</v>
       </c>
       <c r="E28">
-        <v>23.11489028979133</v>
+        <v>16.68865757709036</v>
       </c>
       <c r="F28">
         <v>60.19645213311831</v>
       </c>
       <c r="G28">
-        <v>16.68865757709036</v>
+        <v>23.11489028979133</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.1456613339728</v>
+      </c>
+      <c r="C29">
         <v>35.02106813743962</v>
-      </c>
-      <c r="C29">
-        <v>28.1456613339728</v>
       </c>
       <c r="D29">
         <v>2.855424043822753</v>
       </c>
       <c r="E29">
-        <v>21.46336342641192</v>
+        <v>17.24963258450556</v>
       </c>
       <c r="F29">
         <v>61.28700398908251</v>
       </c>
       <c r="G29">
-        <v>17.24963258450556</v>
+        <v>21.46336342641192</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>27.65716637514147</v>
+      </c>
+      <c r="C30">
         <v>40.42596974997428</v>
-      </c>
-      <c r="C30">
-        <v>27.65716637514147</v>
       </c>
       <c r="D30">
         <v>2.473657419190634</v>
       </c>
       <c r="E30">
-        <v>24.05117531831538</v>
+        <v>16.45445641527914</v>
       </c>
       <c r="F30">
         <v>59.49436826640549</v>
       </c>
       <c r="G30">
-        <v>16.45445641527914</v>
+        <v>24.05117531831538</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>29.44582299421009</v>
+      </c>
+      <c r="C31">
         <v>35.00597371565114</v>
-      </c>
-      <c r="C31">
-        <v>29.44582299421009</v>
       </c>
       <c r="D31">
         <v>2.856655290102389</v>
       </c>
       <c r="E31">
+        <v>17.9054431653068</v>
+      </c>
+      <c r="F31">
+        <v>60.80809209790991</v>
+      </c>
+      <c r="G31">
         <v>21.28646473678328</v>
-      </c>
-      <c r="F31">
-        <v>60.80809209790992</v>
-      </c>
-      <c r="G31">
-        <v>17.90544316530681</v>
       </c>
     </row>
   </sheetData>
